--- a/Asynchronous_FIFO_VPLAN.xlsx
+++ b/Asynchronous_FIFO_VPLAN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SystemVerilog_Learning\Verification_Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SystemVerilog_Learning\Project\Asynchronous_FIFO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523BB1DE-7CB0-4E6B-A0B0-24F74F585467}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7181093C-1740-4A80-BE68-2C9F5BF3400E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Total Items</t>
   </si>
@@ -76,75 +76,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Clock divsor + counter</t>
-  </si>
-  <si>
-    <t>count_up_by_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b01: Clock supply to Counter block will be 100 MHz
-2. Timer_en = 1, count_down = 0; observe 0→255→0; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_up_2</t>
-  </si>
-  <si>
-    <t>count_up_by_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b10: Clock supply to Counter block will be 50 MHz
-2. Timer_en = 1, count_down = 0; observe 0→255→0; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_up_4</t>
-  </si>
-  <si>
-    <t>count_up_by_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b11: Clock supply to Counter block will be 25 MHz
-2. Timer_en = 1, count_down = 0; observe 0→255→0; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_up_8</t>
-  </si>
-  <si>
-    <t>count_down_by_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b01: Clock supply to Counter block will be 100 MHz
-2. Timer_en = 1, count_down = 1; observe 255→ 0 → 255; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_down_2</t>
-  </si>
-  <si>
-    <t>count_down_by_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b10: Clock supply to Counter block will be 50 MHz
-2. Timer_en = 1, count_down = 1; observe 255→ 0 → 255; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_down_4</t>
-  </si>
-  <si>
-    <t>count_down_by_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. clk_div = 2’b11: Clock supply to Counter block will be 25 MHz
-2. Timer_en = 1, count_down = 1; observe 255→ 0 → 255; overflow set
-</t>
-  </si>
-  <si>
-    <t>count_down_8</t>
   </si>
   <si>
     <t>Reset test</t>
@@ -325,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -336,9 +267,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -851,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -867,13 +795,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>48</v>
+      <c r="D9" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>14</v>
@@ -891,13 +819,13 @@
         <v>1.2</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>16</v>
@@ -908,14 +836,14 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1">
       <c r="A11" s="4">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -931,13 +859,13 @@
         <v>2.1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>58</v>
+        <v>22</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>14</v>
@@ -955,13 +883,13 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>59</v>
+        <v>23</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>14</v>
@@ -979,13 +907,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>14</v>
@@ -1003,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1019,13 +947,13 @@
         <v>3.1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>61</v>
+        <v>25</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>14</v>
@@ -1043,13 +971,13 @@
         <v>3.2</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>62</v>
+        <v>26</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>14</v>
@@ -1067,7 +995,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1083,13 +1011,13 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>63</v>
+        <v>28</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>16</v>
@@ -1103,213 +1031,38 @@
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="48" customHeight="1">
-      <c r="A20" s="4">
-        <v>5</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A21" s="5">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="46.9" customHeight="1">
-      <c r="A22" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" ht="46.9" customHeight="1">
-      <c r="A23" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-    </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A24" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A25" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A26" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1">
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1">
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-    </row>
+    <row r="23" spans="1:10" ht="46.9" customHeight="1"/>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1"/>
     <row r="32" spans="1:10" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
